--- a/reports/pdf_rolling5_20260812.xlsx
+++ b/reports/pdf_rolling5_20260812.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K62"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,14 +562,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-08-05 ~ 2026-08-12  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-08-05 ~ 2026-08-12  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,738억   ·   현금 265억(5.5%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 11종목  /  매도 11종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,738억   ·   현금 266억(5.5%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 12종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -658,23 +658,23 @@
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>하림지주  (신규)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>529003200</v>
+        <v>1469918880</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.22%</t>
+          <t>0.00%→0.32%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>211→233</t>
+          <t>0→123</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -683,42 +683,42 @@
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-92</v>
+        <v>-189</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-928552320</v>
+        <v>-1876361760</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>1.72%→1.42%</t>
+          <t>1.72%→1.19%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>737→645</t>
+          <t>737→548</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>926323200</v>
+        <v>987376320</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.38%</t>
+          <t>1.67%→1.92%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>99→116</t>
+          <t>665→749</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -727,1843 +727,2583 @@
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-28</v>
+        <v>-57</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-916003200</v>
+        <v>-1929427200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.80%</t>
+          <t>1.04%→0.61%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>140→112</t>
+          <t>140→83</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>954393600</v>
+        <v>1959768000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.18%</t>
+          <t>0.93%→1.39%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>80→97</t>
+          <t>68→98</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-19</v>
+        <v>-27</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1288245600</v>
+        <v>-466722000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>1.19%→0.81%</t>
+          <t>0.15%→0.05%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>74→55</t>
+          <t>40→13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1448102400</v>
+        <v>3176496000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.27%</t>
+          <t>0.22%→0.90%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>150→166</t>
+          <t>8→35</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>노바렉스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-14</v>
+        <v>-23</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-242726400</v>
+        <v>-1471632000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>0.15%→0.10%</t>
+          <t>1.09%→0.67%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>40→26</t>
+          <t>71→48</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>475545600</v>
+        <v>518786400</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>3.33%→3.40%</t>
+          <t>0.99%→1.20%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>510→526</t>
+          <t>211→233</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-13</v>
+        <v>-19</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-332046000</v>
+        <v>-1194127200</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.20%</t>
+          <t>1.19%→0.75%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>49→36</t>
+          <t>74→55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1662552000</v>
+        <v>914042400</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.55%</t>
+          <t>0.97%→1.14%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>8→23</t>
+          <t>80→97</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1793203200</v>
+        <v>-338754000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.85%→0.42%</t>
+          <t>0.35%→0.20%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>25→13</t>
+          <t>49→36</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>507744000</v>
+        <v>875445600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.19%→1.35%</t>
+          <t>1.26%→1.30%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>112→122</t>
+          <t>99→116</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>원익IPS  (편출)</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-896292000</v>
+        <v>-2011161600</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.00%</t>
+          <t>0.85%→0.47%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>9→0</t>
+          <t>25→13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>435607200</v>
+        <v>1492684800</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.93%→1.02%</t>
+          <t>2.61%→3.37%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>68→75</t>
+          <t>150→166</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>원익IPS  (편출)</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2538720000</v>
+        <v>-896292000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>3.63%→2.95%</t>
+          <t>0.22%→0.00%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>38→32</t>
+          <t>9→0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1795680000</v>
+        <v>467289600</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>4.98%→6.25%</t>
+          <t>3.33%→3.35%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>75→80</t>
+          <t>510→526</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-204955200</v>
+        <v>-299692800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.43%</t>
+          <t>0.65%→0.60%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>43→39</t>
+          <t>82→74</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>525288000</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>1.19%→1.40%</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>112→122</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
           <t>심텍</t>
         </is>
       </c>
-      <c r="B15" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="11" t="n">
-        <v>478435200</v>
-      </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>5.14%→5.65%</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>213→217</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>레인보우로보틱스</t>
-        </is>
-      </c>
       <c r="H15" s="15" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-2018592000</v>
+        <v>-940358400</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.55%</t>
+          <t>5.14%→5.25%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>9→5</t>
+          <t>213→205</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>1689900000</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>4.98%→5.89%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>75→80</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-2582064000</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>3.63%→3.00%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>38→32</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t>피에스케이</t>
         </is>
       </c>
-      <c r="B16" s="11" t="n">
+      <c r="B17" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="11" t="n">
-        <v>410839200</v>
-      </c>
-      <c r="D16" s="12" t="inlineStr">
-        <is>
-          <t>2.29%→2.26%</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="C17" s="11" t="n">
+        <v>399693600</v>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>2.29%→2.21%</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>73→76</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>레인보우로보틱스</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-1981440000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>1.04%→0.54%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>9→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I18" s="15" t="n">
+        <v>-211353600</v>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>0.52%→0.45%</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>43→39</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>로보티즈</t>
         </is>
       </c>
-      <c r="H16" s="15" t="n">
+      <c r="H19" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I16" s="15" t="n">
-        <v>-764712000</v>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>3.35%→3.05%</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
+      <c r="I19" s="15" t="n">
+        <v>-753876000</v>
+      </c>
+      <c r="J19" s="16" t="inlineStr">
+        <is>
+          <t>3.35%→3.01%</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
         <is>
           <t>58→55</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="21" ht="19" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,270억   ·   현금 21억(0.5%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="8" t="n"/>
+      <c r="J22" s="8" t="n"/>
+      <c r="K22" s="8" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G23" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>큐라클</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>106</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>654825600</v>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>1.29%→1.59%</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>986→1,092</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n">
-        <v>-33</v>
-      </c>
-      <c r="I21" s="15" t="n">
-        <v>-2089137600</v>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>5.64%→4.93%</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>363→330</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>앱클론</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>71</v>
-      </c>
-      <c r="C22" s="11" t="n">
-        <v>1300833600</v>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>2.03%→2.65%</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>542→613</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>-23</v>
-      </c>
-      <c r="I22" s="15" t="n">
-        <v>-4226112000</v>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>9.40%→9.80%</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>249→226</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>오스코텍</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="n">
-        <v>63</v>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>1264032000</v>
-      </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>3.19%→3.39%</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>652→715</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>-11</v>
-      </c>
-      <c r="I23" s="15" t="n">
-        <v>-1167408000</v>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>7.80%→7.17%</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>297→286</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>큐라클</t>
         </is>
       </c>
       <c r="B24" s="11" t="n">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>433197600</v>
+        <v>652586880</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.89%</t>
+          <t>1.29%→1.62%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>1,066→1,127</t>
+          <t>986→1,092</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>한미약품</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-7</v>
+        <v>-33</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1506120000</v>
+        <v>-2036865600</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>5.93%→5.28%</t>
+          <t>5.64%→4.91%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>111→104</t>
+          <t>363→330</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>에이비엘바이오</t>
+          <t>앱클론</t>
         </is>
       </c>
       <c r="B25" s="11" t="n">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>2075673600</v>
+        <v>1274592000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>8.58%→9.30%</t>
+          <t>2.03%→2.65%</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>755→797</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="n"/>
-      <c r="I25" s="17" t="n"/>
-      <c r="J25" s="17" t="n"/>
-      <c r="K25" s="17" t="n"/>
+          <t>542→613</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-3977160000</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>9.40%→9.42%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>249→226</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="B26" s="11" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>2109993600</v>
+        <v>1244073600</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>8.65%→9.28%</t>
+          <t>3.19%→3.40%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>511→540</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
+          <t>652→715</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-1222584000</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>7.80%→7.66%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>297→286</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n">
+        <v>61</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>409041600</v>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>1.47%→1.82%</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>1,066→1,127</t>
+        </is>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-1526448000</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>5.93%→5.47%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>111→104</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>1975881600</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>8.58%→9.04%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>755→797</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
+      <c r="K28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>2019652800</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>8.65%→9.07%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>511→540</t>
+        </is>
+      </c>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
           <t>보로노이</t>
         </is>
       </c>
-      <c r="B27" s="11" t="n">
+      <c r="B30" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <v>1210809600</v>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>2.08%→2.64%</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="C30" s="11" t="n">
+        <v>1211496000</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>2.08%→2.70%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>107→120</t>
         </is>
       </c>
-      <c r="G27" s="17" t="n"/>
-      <c r="H27" s="17" t="n"/>
-      <c r="I27" s="17" t="n"/>
-      <c r="J27" s="17" t="n"/>
-      <c r="K27" s="17" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="n"/>
-      <c r="C31" s="19" t="n"/>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="19" t="n"/>
-      <c r="F31" s="19" t="n"/>
-      <c r="G31" s="19" t="n"/>
-      <c r="H31" s="19" t="n"/>
-      <c r="I31" s="19" t="n"/>
-      <c r="J31" s="19" t="n"/>
-      <c r="K31" s="19" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 287억   ·   현금 14억(4.8%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 11종목  /  매도 15종목</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,676억   ·   현금 63억(2.3%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 4종목  /  매도 8종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>4454912000</v>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>1.42%→3.32%</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>69→139</t>
+        </is>
+      </c>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-281</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-1903066880</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>1.38%→0.55%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>499→218</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="B36" s="11" t="n">
-        <v>224</v>
+        <v>50</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>421344000</v>
+        <v>4012800000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>5.34%→6.85%</t>
+          <t>1.60%→3.01%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>796→1,020</t>
+          <t>50→100</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>에이프로</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>-199</v>
+        <v>-148</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-50892260</v>
+        <v>-3490432000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.21%</t>
+          <t>2.38%→1.33%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>427→228</t>
+          <t>298→150</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>심텍홀딩스</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>20732800</v>
+        <v>534927360</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.65%→0.73%</t>
+          <t>0.17%→0.41%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>547→609</t>
+          <t>50→98</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>더블유씨피</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>-184</v>
+        <v>-122</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-118304640</v>
+        <v>-2430630400</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>7.87%→7.45%</t>
+          <t>1.86%→0.89%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>3,430→3,246</t>
+          <t>241→119</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B38" s="11" t="n">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>77580800</v>
+        <v>7608480000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>2.97%→3.25%</t>
+          <t>3.93%→7.19%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>622→680</t>
+          <t>50→83</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>브이엠</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>-117</v>
+        <v>-34</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-223189200</v>
+        <v>-1732966400</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>3.50%→2.70%</t>
+          <t>2.94%→2.20%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>514→397</t>
+          <t>149→115</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>133771400</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>7.11%→7.59%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>700→747</t>
-        </is>
-      </c>
+      <c r="A39" s="17" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>상신이디피</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-65</v>
+        <v>-23</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-88327200</v>
+        <v>-2090387200</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>1.69%→1.38%</t>
+          <t>2.23%→1.26%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>349→284</t>
+          <t>60→37</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>코스맥스엔비티  (신규)</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>29275200</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.10%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>0→36</t>
-        </is>
-      </c>
+      <c r="A40" s="17" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>금양그린파워</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-53</v>
+        <v>-20</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-32425400</v>
+        <v>-992640000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.82%→0.70%</t>
+          <t>1.90%→1.49%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>375→322</t>
+          <t>100→80</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>노바렉스  (신규)</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>28089600</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.10%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>0→22</t>
-        </is>
-      </c>
+      <c r="A41" s="17" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>오로스테크놀로지</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-38</v>
+        <v>-5</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-41962640</v>
+        <v>-1467840000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.25%→0.10%</t>
+          <t>2.04%→1.43%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>63→25</t>
+          <t>18→13</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>엘티씨</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>46968000</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>0.99%→1.16%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>89→104</t>
-        </is>
-      </c>
+      <c r="A42" s="17" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>상아프론테크</t>
+          <t>미래에셋벤처투자</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-29</v>
+        <v>-3</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-31869840</v>
+        <v>-35418240</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.42%→0.31%</t>
+          <t>0.55%→0.56%</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>107→78</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>오이솔루션</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>29579200</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>0.11%→0.21%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>14→28</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>네패스아크</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-24</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-48700800</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>0.27%→0.09%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>37→13</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이홀딩스</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>47880000</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>2.73%→2.91%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>96→102</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>원익머트리얼즈</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-48632400</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>2.59%→2.42%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>269→251</t>
-        </is>
-      </c>
+          <t>129→126</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,463억   ·   현금 30억(1.2%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 4종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>피에스케이</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>60511200</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>2.95%→3.17%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>82→88</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-36966400</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>2.78%→2.65%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>337→321</t>
-        </is>
-      </c>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="8" t="n"/>
+      <c r="J45" s="8" t="n"/>
+      <c r="K45" s="8" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>파두</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>27998400</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>0.88%→0.98%</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>53→59</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>솔브레인홀딩스</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-38087400</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>0.72%→0.59%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>69→56</t>
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>106</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>4711731800</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>6.15%→8.05%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>329→435</t>
+        </is>
+      </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>일동제약</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-8</v>
+        <v>-184</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-36662400</v>
+        <v>-965464560</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.77%</t>
+          <t>0.92%→0.47%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>55→47</t>
+          <t>400→216</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>2512335000</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>0.89%→2.03%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>99→204</t>
+        </is>
+      </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>HK이노엔</t>
+          <t>네이처셀</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-7</v>
+        <v>-160</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-22610000</v>
+        <v>-1261728000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.13%→0.05%</t>
+          <t>0.69%→0.14%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>11→4</t>
+          <t>202→42</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>3506181700</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>5.14%→6.38%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>300→389</t>
+        </is>
+      </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HK이노엔  (편출)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
-        <v>-7</v>
+        <v>-102</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-61658800</v>
+        <v>-1337148600</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>2.48%→2.26%</t>
+          <t>0.62%→0.00%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>79→72</t>
+          <t>102→0</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>2438700500</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>1.29%→2.50%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>60→101</t>
+        </is>
+      </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>HPSP</t>
+          <t>펩트론  (편출)</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-3</v>
+        <v>-76</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-8424600</v>
+        <v>-4451365600</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>1.24%→1.21%</t>
+          <t>2.06%→0.00%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>124→121</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="19" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 621억   ·   현금 19억(3.1%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 6종목  /  매도 4종목</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+          <t>76→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="n"/>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-72</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-5107572000</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>10.75%→8.83%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>371→299</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="19" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 287억   ·   현금 14억(4.8%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 11종목  /  매도 15종목</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="G53" s="7" t="inlineStr">
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n"/>
+      <c r="E54" s="6" t="n"/>
+      <c r="G54" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="8" t="n"/>
+      <c r="J54" s="8" t="n"/>
+      <c r="K54" s="8" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C54" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D55" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="G55" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H55" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
+      <c r="I55" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="K55" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>오름테라퓨틱  (신규)</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="n">
-        <v>179</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>1451403600</v>
-      </c>
-      <c r="D55" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→2.44%</t>
-        </is>
-      </c>
-      <c r="E55" s="13" t="inlineStr">
-        <is>
-          <t>0→179</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-77</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>-586832400</v>
-      </c>
-      <c r="J55" s="16" t="inlineStr">
-        <is>
-          <t>7.47%→5.69%</t>
-        </is>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>522→445</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>앱클론</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="B56" s="11" t="n">
-        <v>168</v>
+        <v>224</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>676233600</v>
+        <v>421344000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>2.61%→4.15%</t>
+          <t>5.34%→6.85%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>446→614</t>
+          <t>796→1,020</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>에이프로</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-24</v>
+        <v>-199</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1141440000</v>
+        <v>-50892260</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>6.20%→3.91%</t>
+          <t>0.39%→0.21%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>73→49</t>
+          <t>427→228</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>심텍홀딩스</t>
         </is>
       </c>
       <c r="B57" s="11" t="n">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>556452000</v>
+        <v>20732800</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>2.56%→3.58%</t>
+          <t>0.65%→0.73%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>368→498</t>
+          <t>547→609</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>휴젤</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
-        <v>-22</v>
+        <v>-184</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-713284000</v>
+        <v>-118304640</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>5.07%→3.65%</t>
+          <t>7.87%→7.45%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>89→67</t>
+          <t>3,430→3,246</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>132240000</v>
+        <v>77580800</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>3.63%→3.74%</t>
+          <t>2.97%→3.25%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>475→505</t>
+          <t>622→680</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-21</v>
+        <v>-117</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-847728000</v>
+        <v>-223189200</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>9.44%→9.42%</t>
+          <t>3.50%→2.70%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>160→139</t>
+          <t>514→397</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>보로노이</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>552484800</v>
+        <v>133771400</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>1.88%→3.06%</t>
+          <t>7.11%→7.59%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>62→89</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="n"/>
-      <c r="H59" s="17" t="n"/>
-      <c r="I59" s="17" t="n"/>
-      <c r="J59" s="17" t="n"/>
-      <c r="K59" s="17" t="n"/>
+          <t>700→747</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>상신이디피</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-65</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-88327200</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>1.69%→1.38%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>349→284</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
+          <t>코스맥스엔비티  (신규)</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>29275200</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.10%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>0→36</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>금양그린파워</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-32425400</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>0.82%→0.70%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>375→322</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>노바렉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>28089600</v>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.10%</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>0→22</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-38</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-41962640</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>0.25%→0.10%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>63→25</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>46968000</v>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>0.99%→1.16%</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>89→104</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>상아프론테크</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-31869840</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.31%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>107→78</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>29579200</v>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>0.11%→0.21%</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>14→28</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-48700800</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>0.27%→0.09%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>37→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>60511200</v>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>2.95%→3.17%</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>82→88</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>원익머트리얼즈</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-48632400</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>2.59%→2.42%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>269→251</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>27998400</v>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>0.88%→0.98%</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>53→59</t>
+        </is>
+      </c>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-36966400</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>2.78%→2.65%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>337→321</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>47880000</v>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>2.73%→2.91%</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>96→102</t>
+        </is>
+      </c>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-38087400</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>0.72%→0.59%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>69→56</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="n"/>
+      <c r="B67" s="17" t="n"/>
+      <c r="C67" s="17" t="n"/>
+      <c r="D67" s="17" t="n"/>
+      <c r="E67" s="17" t="n"/>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>하나머티리얼즈</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-36662400</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>0.90%→0.77%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>55→47</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="n"/>
+      <c r="B68" s="17" t="n"/>
+      <c r="C68" s="17" t="n"/>
+      <c r="D68" s="17" t="n"/>
+      <c r="E68" s="17" t="n"/>
+      <c r="G68" s="14" t="inlineStr">
+        <is>
+          <t>HK이노엔</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I68" s="15" t="n">
+        <v>-22610000</v>
+      </c>
+      <c r="J68" s="16" t="inlineStr">
+        <is>
+          <t>0.13%→0.05%</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>11→4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="n"/>
+      <c r="B69" s="17" t="n"/>
+      <c r="C69" s="17" t="n"/>
+      <c r="D69" s="17" t="n"/>
+      <c r="E69" s="17" t="n"/>
+      <c r="G69" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I69" s="15" t="n">
+        <v>-61658800</v>
+      </c>
+      <c r="J69" s="16" t="inlineStr">
+        <is>
+          <t>2.48%→2.26%</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>79→72</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="17" t="n"/>
+      <c r="B70" s="17" t="n"/>
+      <c r="C70" s="17" t="n"/>
+      <c r="D70" s="17" t="n"/>
+      <c r="E70" s="17" t="n"/>
+      <c r="G70" s="14" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I70" s="15" t="n">
+        <v>-8424600</v>
+      </c>
+      <c r="J70" s="16" t="inlineStr">
+        <is>
+          <t>1.24%→1.21%</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>124→121</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 621억   ·   현금 19억(3.2%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 6종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+      <c r="E73" s="6" t="n"/>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="8" t="n"/>
+      <c r="J73" s="8" t="n"/>
+      <c r="K73" s="8" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K74" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱  (신규)</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>179</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>1474244000</v>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.52%</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>0→179</t>
+        </is>
+      </c>
+      <c r="G75" s="14" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n">
+        <v>-77</v>
+      </c>
+      <c r="I75" s="15" t="n">
+        <v>-543958800</v>
+      </c>
+      <c r="J75" s="16" t="inlineStr">
+        <is>
+          <t>7.47%→5.38%</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>522→445</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>168</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>662592000</v>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>2.61%→4.14%</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>446→614</t>
+        </is>
+      </c>
+      <c r="G76" s="14" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I76" s="15" t="n">
+        <v>-1160928000</v>
+      </c>
+      <c r="J76" s="16" t="inlineStr">
+        <is>
+          <t>6.20%→4.06%</t>
+        </is>
+      </c>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>73→49</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>527046000</v>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>2.56%→3.45%</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>368→498</t>
+        </is>
+      </c>
+      <c r="G77" s="14" t="inlineStr">
+        <is>
+          <t>휴젤</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I77" s="15" t="n">
+        <v>-720940000</v>
+      </c>
+      <c r="J77" s="16" t="inlineStr">
+        <is>
+          <t>5.07%→3.76%</t>
+        </is>
+      </c>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>89→67</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>오스코텍</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>130152000</v>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>3.63%→3.75%</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>475→505</t>
+        </is>
+      </c>
+      <c r="G78" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I78" s="15" t="n">
+        <v>-797790000</v>
+      </c>
+      <c r="J78" s="16" t="inlineStr">
+        <is>
+          <t>9.44%→9.04%</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>160→139</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>552798000</v>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>1.88%→3.12%</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>62→89</t>
+        </is>
+      </c>
+      <c r="G79" s="17" t="n"/>
+      <c r="H79" s="17" t="n"/>
+      <c r="I79" s="17" t="n"/>
+      <c r="J79" s="17" t="n"/>
+      <c r="K79" s="17" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
           <t>에스티팜</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
+      <c r="B80" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="C60" s="11" t="n">
+      <c r="C80" s="11" t="n">
         <v>263088000</v>
       </c>
-      <c r="D60" s="12" t="inlineStr">
-        <is>
-          <t>5.23%→5.38%</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>5.23%→5.49%</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>235→256</t>
         </is>
       </c>
-      <c r="G60" s="17" t="n"/>
-      <c r="H60" s="17" t="n"/>
-      <c r="I60" s="17" t="n"/>
-      <c r="J60" s="17" t="n"/>
-      <c r="K60" s="17" t="n"/>
-    </row>
-    <row r="62" ht="19" customHeight="1">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="G80" s="17" t="n"/>
+      <c r="H80" s="17" t="n"/>
+      <c r="I80" s="17" t="n"/>
+      <c r="J80" s="17" t="n"/>
+      <c r="K80" s="17" t="n"/>
+    </row>
+    <row r="82" ht="19" customHeight="1">
+      <c r="A82" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B62" s="19" t="n"/>
-      <c r="C62" s="19" t="n"/>
-      <c r="D62" s="19" t="n"/>
-      <c r="E62" s="19" t="n"/>
-      <c r="F62" s="19" t="n"/>
-      <c r="G62" s="19" t="n"/>
-      <c r="H62" s="19" t="n"/>
-      <c r="I62" s="19" t="n"/>
-      <c r="J62" s="19" t="n"/>
-      <c r="K62" s="19" t="n"/>
+      <c r="B82" s="19" t="n"/>
+      <c r="C82" s="19" t="n"/>
+      <c r="D82" s="19" t="n"/>
+      <c r="E82" s="19" t="n"/>
+      <c r="F82" s="19" t="n"/>
+      <c r="G82" s="19" t="n"/>
+      <c r="H82" s="19" t="n"/>
+      <c r="I82" s="19" t="n"/>
+      <c r="J82" s="19" t="n"/>
+      <c r="K82" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A34:E34"/>
+  <mergeCells count="21">
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A82:K82"/>
+    <mergeCell ref="A45:E45"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A21:K21"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="G45:K45"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="G73:K73"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A53:K53"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A33:K33"/>
-    <mergeCell ref="A52:K52"/>
-    <mergeCell ref="G19:K19"/>
-    <mergeCell ref="G53:K53"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A72:K72"/>
+    <mergeCell ref="G54:K54"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="G22:K22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260812.xlsx
+++ b/reports/pdf_rolling5_20260812.xlsx
@@ -878,23 +878,23 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
         <v>17</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>914042400</v>
+        <v>875445600</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.14%</t>
+          <t>1.26%→1.30%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>80→97</t>
+          <t>99→116</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -922,23 +922,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>875445600</v>
+        <v>914042400</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.26%→1.30%</t>
+          <t>0.97%→1.14%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>99→116</t>
+          <t>80→97</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1492684800</v>
+        <v>467289600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.37%</t>
+          <t>3.33%→3.35%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>150→166</t>
+          <t>510→526</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>467289600</v>
+        <v>1492684800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.33%→3.35%</t>
+          <t>2.61%→3.37%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>510→526</t>
+          <t>150→166</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2702,23 +2702,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>60511200</v>
+        <v>47880000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.17%</t>
+          <t>2.73%→2.91%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2790,23 +2790,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>47880000</v>
+        <v>60511200</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.73%→2.91%</t>
+          <t>2.95%→3.17%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2867,23 +2867,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>HK이노엔</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-22610000</v>
+        <v>-61658800</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.13%→0.05%</t>
+          <t>2.48%→2.26%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>11→4</t>
+          <t>79→72</t>
         </is>
       </c>
     </row>
@@ -2895,23 +2895,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HK이노엔</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-61658800</v>
+        <v>-22610000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2.48%→2.26%</t>
+          <t>0.13%→0.05%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>79→72</t>
+          <t>11→4</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260812.xlsx
+++ b/reports/pdf_rolling5_20260812.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,738억   ·   현금 266억(5.5%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 12종목  /  매도 14종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,732억   ·   현금 267억(5.5%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 12종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>123</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1469918880</v>
+        <v>1472767560</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-189</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1876361760</v>
+        <v>-1879998120</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>84</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>987376320</v>
+        <v>989289840</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-57</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1929427200</v>
+        <v>-1933166400</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>30</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1959768000</v>
+        <v>1963566000</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-27</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-466722000</v>
+        <v>-467626500</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3176496000</v>
+        <v>3182652000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-23</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-1471632000</v>
+        <v>-1474484000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>518786400</v>
+        <v>519791800</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-19</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1194127200</v>
+        <v>-1196441400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>875445600</v>
+        <v>877142200</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-13</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-338754000</v>
+        <v>-339410500</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>17</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>914042400</v>
+        <v>915813800</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2011161600</v>
+        <v>-2015059200</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>467289600</v>
+        <v>1495577600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.33%→3.35%</t>
+          <t>2.61%→3.37%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>510→526</t>
+          <t>150→166</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>-9</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-896292000</v>
+        <v>-898029000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1492684800</v>
+        <v>468195200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.37%</t>
+          <t>3.33%→3.35%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>150→166</t>
+          <t>510→526</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1038,7 +1038,7 @@
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-299692800</v>
+        <v>-300273600</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>525288000</v>
+        <v>526306000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-8</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-940358400</v>
+        <v>-942180800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>5</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>1689900000</v>
+        <v>1693175000</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-2582064000</v>
+        <v>-2587068000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>399693600</v>
+        <v>400468200</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1981440000</v>
+        <v>-1985280000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-211353600</v>
+        <v>-211763200</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>-3</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-753876000</v>
+        <v>-755337000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,270억   ·   현금 21억(0.5%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 7종목  /  매도 4종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,183억   ·   현금 21억(0.5%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1338,7 +1338,7 @@
         <v>106</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>652586880</v>
+        <v>656294760</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>-33</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-2036865600</v>
+        <v>-2048438700</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>71</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1274592000</v>
+        <v>1281834000</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>-23</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-3977160000</v>
+        <v>-3999757500</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>63</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>1244073600</v>
+        <v>1251142200</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>-11</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-1222584000</v>
+        <v>-1229530500</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>61</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>409041600</v>
+        <v>411365700</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>-7</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-1526448000</v>
+        <v>-1535121000</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>42</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>1975881600</v>
+        <v>1987108200</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>29</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>2019652800</v>
+        <v>2031128100</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>13</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1211496000</v>
+        <v>1218379500</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,676억   ·   현금 63억(2.3%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 4종목  /  매도 8종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,694억   ·   현금 63억(2.3%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 4종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -1687,7 +1687,7 @@
         <v>70</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>4454912000</v>
+        <v>4442256000</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>-281</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1903066880</v>
+        <v>-1897660440</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>50</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>4012800000</v>
+        <v>4001400000</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>-148</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-3490432000</v>
+        <v>-3480516000</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>48</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>534927360</v>
+        <v>533407680</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>-122</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-2430630400</v>
+        <v>-2423725200</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         <v>33</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>7608480000</v>
+        <v>7586865000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>-34</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1732966400</v>
+        <v>-1728043200</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>-23</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2090387200</v>
+        <v>-2084448600</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>-20</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-992640000</v>
+        <v>-989820000</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>-5</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-1467840000</v>
+        <v>-1463670000</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>-3</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-35418240</v>
+        <v>-35317620</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
     <row r="44" ht="19" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,463억   ·   현금 30억(1.2%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,418억   ·   현금 30억(1.2%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B44" s="4" t="n"/>
@@ -2064,7 +2064,7 @@
         <v>106</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>4711731800</v>
+        <v>4725713200</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>-184</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-965464560</v>
+        <v>-968329440</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>105</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>2512335000</v>
+        <v>2519790000</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>-160</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-1261728000</v>
+        <v>-1265472000</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>89</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>3506181700</v>
+        <v>3516585800</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         <v>-102</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-1337148600</v>
+        <v>-1341116400</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>41</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>2438700500</v>
+        <v>2445937000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>-76</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-4451365600</v>
+        <v>-4464574400</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>-72</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-5107572000</v>
+        <v>-5122728000</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 287억   ·   현금 14억(4.8%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 11종목  /  매도 15종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 291억   ·   현금 14억(4.7%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 11종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B53" s="4" t="n"/>
@@ -2357,11 +2357,11 @@
         <v>224</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>421344000</v>
+        <v>429856000</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>5.34%→6.85%</t>
+          <t>5.37%→6.89%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -2378,11 +2378,11 @@
         <v>-199</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-50892260</v>
+        <v>-51043500</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.39%→0.21%</t>
+          <t>0.38%→0.21%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2401,11 +2401,11 @@
         <v>62</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>20732800</v>
+        <v>19460560</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>0.65%→0.73%</t>
+          <t>0.60%→0.67%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2422,11 +2422,11 @@
         <v>-184</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-118304640</v>
+        <v>-121800640</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>7.87%→7.45%</t>
+          <t>7.98%→7.56%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2445,11 +2445,11 @@
         <v>58</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>77580800</v>
+        <v>79255840</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.97%→3.25%</t>
+          <t>2.99%→3.27%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -2466,11 +2466,11 @@
         <v>-117</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-223189200</v>
+        <v>-225412200</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>3.50%→2.70%</t>
+          <t>3.48%→2.69%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2489,11 +2489,11 @@
         <v>47</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>133771400</v>
+        <v>136807600</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>7.11%→7.59%</t>
+          <t>7.16%→7.65%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -2510,11 +2510,11 @@
         <v>-65</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-88327200</v>
+        <v>-89364600</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>1.69%→1.38%</t>
+          <t>1.69%→1.37%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2533,7 +2533,7 @@
         <v>36</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>29275200</v>
+        <v>28509120</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2554,11 +2554,11 @@
         <v>-53</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-32425400</v>
+        <v>-31901760</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.82%→0.70%</t>
+          <t>0.79%→0.68%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2577,7 +2577,7 @@
         <v>22</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>28089600</v>
+        <v>28006000</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>-38</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-41962640</v>
+        <v>-42540240</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2621,11 +2621,11 @@
         <v>15</v>
       </c>
       <c r="C62" s="11" t="n">
-        <v>46968000</v>
+        <v>47139000</v>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>0.99%→1.16%</t>
+          <t>0.98%→1.15%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -2642,7 +2642,7 @@
         <v>-29</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-31869840</v>
+        <v>-32354720</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2665,11 +2665,11 @@
         <v>14</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>29579200</v>
+        <v>26972400</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>0.11%→0.21%</t>
+          <t>0.09%→0.19%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -2686,11 +2686,11 @@
         <v>-24</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-48700800</v>
+        <v>-51892800</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.09%</t>
+          <t>0.28%→0.10%</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -2702,23 +2702,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>47880000</v>
+        <v>58869600</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.73%→2.91%</t>
+          <t>2.83%→3.04%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2730,11 +2730,11 @@
         <v>-18</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-48632400</v>
+        <v>-49795200</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>2.59%→2.42%</t>
+          <t>2.62%→2.44%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
@@ -2746,23 +2746,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>27998400</v>
+        <v>49749600</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.88%→0.98%</t>
+          <t>2.80%→2.98%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -2774,11 +2774,11 @@
         <v>-16</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-36966400</v>
+        <v>-40736000</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>2.78%→2.65%</t>
+          <t>3.02%→2.88%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
@@ -2790,23 +2790,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>60511200</v>
+        <v>28272000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.17%</t>
+          <t>0.88%→0.98%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2818,11 +2818,11 @@
         <v>-13</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-38087400</v>
+        <v>-40261000</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.59%</t>
+          <t>0.75%→0.61%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -2846,11 +2846,11 @@
         <v>-8</v>
       </c>
       <c r="I67" s="15" t="n">
-        <v>-36662400</v>
+        <v>-38486400</v>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>0.90%→0.77%</t>
+          <t>0.93%→0.80%</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
@@ -2874,11 +2874,11 @@
         <v>-7</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-61658800</v>
+        <v>-60594800</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.48%→2.26%</t>
+          <t>2.40%→2.19%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
@@ -2902,11 +2902,11 @@
         <v>-7</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-22610000</v>
+        <v>-22477000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.13%→0.05%</t>
+          <t>0.12%→0.05%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
@@ -2930,11 +2930,11 @@
         <v>-3</v>
       </c>
       <c r="I70" s="15" t="n">
-        <v>-8424600</v>
+        <v>-8755200</v>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>1.24%→1.21%</t>
+          <t>1.27%→1.24%</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="72" ht="19" customHeight="1">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 621억   ·   현금 19억(3.2%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 6종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 20억(3.2%)      오늘 2026-08-12  vs  5일전 2026-08-05      매수 6종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B72" s="4" t="n"/>
@@ -3042,7 +3042,7 @@
         <v>179</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>1474244000</v>
+        <v>1512371000</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>-77</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-543958800</v>
+        <v>-558026700</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>168</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>662592000</v>
+        <v>679728000</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
         <v>-24</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-1160928000</v>
+        <v>-1190952000</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>130</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>527046000</v>
+        <v>540676500</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>-22</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-720940000</v>
+        <v>-739585000</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>30</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>130152000</v>
+        <v>133518000</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>-21</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-797790000</v>
+        <v>-818422500</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
         <v>27</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>552798000</v>
+        <v>567094500</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>21</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>263088000</v>
+        <v>269892000</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260812.xlsx
+++ b/reports/pdf_rolling5_20260812.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1495577600</v>
+        <v>468195200</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.37%</t>
+          <t>3.33%→3.35%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>150→166</t>
+          <t>510→526</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,44 +1010,44 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>468195200</v>
+        <v>1495577600</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>3.33%→3.35%</t>
+          <t>2.61%→3.37%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>510→526</t>
+          <t>150→166</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-300273600</v>
+        <v>-942180800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.60%</t>
+          <t>5.14%→5.25%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>82→74</t>
+          <t>213→205</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-942180800</v>
+        <v>-300273600</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>5.14%→5.25%</t>
+          <t>0.65%→0.60%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>213→205</t>
+          <t>82→74</t>
         </is>
       </c>
     </row>
@@ -1163,23 +1163,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1985280000</v>
+        <v>-211763200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.54%</t>
+          <t>0.52%→0.45%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>9→5</t>
+          <t>43→39</t>
         </is>
       </c>
     </row>
@@ -1191,23 +1191,23 @@
       <c r="E18" s="17" t="n"/>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-211763200</v>
+        <v>-1985280000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.45%</t>
+          <t>1.04%→0.54%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>43→39</t>
+          <t>9→5</t>
         </is>
       </c>
     </row>
@@ -2702,23 +2702,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>58869600</v>
+        <v>49749600</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>2.83%→3.04%</t>
+          <t>2.80%→2.98%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>96→102</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2746,23 +2746,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>49749600</v>
+        <v>28272000</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>2.80%→2.98%</t>
+          <t>0.88%→0.98%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>96→102</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -2790,23 +2790,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>28272000</v>
+        <v>58869600</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>0.88%→0.98%</t>
+          <t>2.83%→3.04%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2867,23 +2867,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HK이노엔</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-60594800</v>
+        <v>-22477000</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.19%</t>
+          <t>0.12%→0.05%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>79→72</t>
+          <t>11→4</t>
         </is>
       </c>
     </row>
@@ -2895,23 +2895,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>HK이노엔</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-22477000</v>
+        <v>-60594800</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.05%</t>
+          <t>2.40%→2.19%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>11→4</t>
+          <t>79→72</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260812.xlsx
+++ b/reports/pdf_rolling5_20260812.xlsx
@@ -966,23 +966,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>468195200</v>
+        <v>1495577600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.33%→3.35%</t>
+          <t>2.61%→3.37%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>510→526</t>
+          <t>150→166</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1010,23 +1010,23 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
         <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1495577600</v>
+        <v>468195200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.37%</t>
+          <t>3.33%→3.35%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>150→166</t>
+          <t>510→526</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2746,23 +2746,23 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B65" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>28272000</v>
+        <v>58869600</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>0.88%→0.98%</t>
+          <t>2.83%→3.04%</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>53→59</t>
+          <t>82→88</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -2790,23 +2790,23 @@
     <row r="66">
       <c r="A66" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B66" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>58869600</v>
+        <v>28272000</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
-          <t>2.83%→3.04%</t>
+          <t>0.88%→0.98%</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>82→88</t>
+          <t>53→59</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -2867,23 +2867,23 @@
       <c r="E68" s="17" t="n"/>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>HK이노엔</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I68" s="15" t="n">
-        <v>-22477000</v>
+        <v>-60594800</v>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.12%→0.05%</t>
+          <t>2.40%→2.19%</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>11→4</t>
+          <t>79→72</t>
         </is>
       </c>
     </row>
@@ -2895,23 +2895,23 @@
       <c r="E69" s="17" t="n"/>
       <c r="G69" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HK이노엔</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
         <v>-7</v>
       </c>
       <c r="I69" s="15" t="n">
-        <v>-60594800</v>
+        <v>-22477000</v>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>2.40%→2.19%</t>
+          <t>0.12%→0.05%</t>
         </is>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>79→72</t>
+          <t>11→4</t>
         </is>
       </c>
     </row>
